--- a/04_Figures/F04_association/modules/trajectory/lm/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/trajectory/lm/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -71,12 +71,6 @@
     <t xml:space="preserve">ME_red@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T1</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_turquoise@T1</t>
   </si>
   <si>
@@ -110,12 +104,6 @@
     <t xml:space="preserve">ME_red@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_turquoise@T2</t>
   </si>
   <si>
@@ -147,12 +135,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T3</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise@T3</t>
@@ -566,16 +548,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3736226927952</v>
+        <v>-6.89822585819254</v>
       </c>
       <c r="E2" t="n">
-        <v>0.224479475323752</v>
+        <v>-0.426693102886649</v>
       </c>
       <c r="F2" t="n">
-        <v>0.826161014004043</v>
+        <v>0.67715780351721</v>
       </c>
       <c r="G2" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="3">
@@ -589,16 +571,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.89684217607248</v>
+        <v>32.96185891895</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.337000302600036</v>
+        <v>1.03957862072391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.741937538776844</v>
+        <v>0.319029296192606</v>
       </c>
       <c r="G3" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="4">
@@ -612,16 +594,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-17.4867284730919</v>
+        <v>1.53619552636473</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.933274289529186</v>
+        <v>0.0949804437860401</v>
       </c>
       <c r="F4" t="n">
-        <v>0.369077262711026</v>
+        <v>0.925897977232582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="5">
@@ -635,16 +617,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>30.8622872138857</v>
+        <v>3.08243408937827</v>
       </c>
       <c r="E5" t="n">
-        <v>0.874312082704751</v>
+        <v>0.227861937856787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.39910861810587</v>
+        <v>0.82358986298878</v>
       </c>
       <c r="G5" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="6">
@@ -658,16 +640,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-14.0057692422702</v>
+        <v>-15.6328440618094</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.974428037667886</v>
+        <v>-1.09490224333587</v>
       </c>
       <c r="F6" t="n">
-        <v>0.349078273151691</v>
+        <v>0.29504912311895</v>
       </c>
       <c r="G6" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="7">
@@ -681,16 +663,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>18.293131689022</v>
+        <v>2.75285687988993</v>
       </c>
       <c r="E7" t="n">
-        <v>1.34617071480301</v>
+        <v>0.182906340510107</v>
       </c>
       <c r="F7" t="n">
-        <v>0.20312702151698</v>
+        <v>0.857925353018268</v>
       </c>
       <c r="G7" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="8">
@@ -704,16 +686,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>1.33199935874961</v>
+        <v>5.61060650989582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.083252745701885</v>
+        <v>0.285839171010082</v>
       </c>
       <c r="F8" t="n">
-        <v>0.935023234757188</v>
+        <v>0.779875617000343</v>
       </c>
       <c r="G8" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="9">
@@ -727,16 +709,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.57364259368531</v>
+        <v>3.39020423983291</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0883082117704903</v>
+        <v>0.248351167508015</v>
       </c>
       <c r="F9" t="n">
-        <v>0.931088342046809</v>
+        <v>0.808061880216599</v>
       </c>
       <c r="G9" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="10">
@@ -750,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>3.14926442973564</v>
+        <v>4.69084018377595</v>
       </c>
       <c r="E10" t="n">
-        <v>0.233687811136958</v>
+        <v>0.390226658312796</v>
       </c>
       <c r="F10" t="n">
-        <v>0.819166399545862</v>
+        <v>0.70320723129057</v>
       </c>
       <c r="G10" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="11">
@@ -773,16 +755,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8075331261171</v>
+        <v>-3.56740307857202</v>
       </c>
       <c r="E11" t="n">
-        <v>0.752670574784579</v>
+        <v>-0.22344575717941</v>
       </c>
       <c r="F11" t="n">
-        <v>0.466157222906084</v>
+        <v>0.82694720805431</v>
       </c>
       <c r="G11" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="12">
@@ -796,16 +778,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>22.5854699034149</v>
+        <v>-16.6842345890006</v>
       </c>
       <c r="E12" t="n">
-        <v>1.12185220443422</v>
+        <v>-0.896018886055482</v>
       </c>
       <c r="F12" t="n">
-        <v>0.283872128598978</v>
+        <v>0.387863904074735</v>
       </c>
       <c r="G12" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="13">
@@ -819,16 +801,16 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.26449682622212</v>
+        <v>1.92456115643549</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.267571659209039</v>
+        <v>0.0752024110112946</v>
       </c>
       <c r="F13" t="n">
-        <v>0.79357250176376</v>
+        <v>0.941292823982978</v>
       </c>
       <c r="G13" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="14">
@@ -842,16 +824,16 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>5.37569123214016</v>
+        <v>4.63992290078818</v>
       </c>
       <c r="E14" t="n">
-        <v>0.402048752013903</v>
+        <v>0.257537379957057</v>
       </c>
       <c r="F14" t="n">
-        <v>0.694717017036974</v>
+        <v>0.801127197874743</v>
       </c>
       <c r="G14" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="15">
@@ -865,16 +847,16 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>2.22597714367282</v>
+        <v>21.9225037729109</v>
       </c>
       <c r="E15" t="n">
-        <v>0.137743871191296</v>
+        <v>1.16533113267041</v>
       </c>
       <c r="F15" t="n">
-        <v>0.892727133223007</v>
+        <v>0.26652672992411</v>
       </c>
       <c r="G15" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="16">
@@ -888,16 +870,16 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>17.569445898295</v>
+        <v>-7.49181951567495</v>
       </c>
       <c r="E16" t="n">
-        <v>0.802761091155143</v>
+        <v>-0.378727396021366</v>
       </c>
       <c r="F16" t="n">
-        <v>0.437723743452316</v>
+        <v>0.711505906523031</v>
       </c>
       <c r="G16" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="17">
@@ -911,16 +893,16 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.30759950098749</v>
+        <v>0.949974465438548</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.223642227166733</v>
+        <v>0.0527472489383167</v>
       </c>
       <c r="F17" t="n">
-        <v>0.826797767752449</v>
+        <v>0.958801220623954</v>
       </c>
       <c r="G17" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="18">
@@ -934,16 +916,16 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>7.73918152472429</v>
+        <v>1.5712805667871</v>
       </c>
       <c r="E18" t="n">
-        <v>0.35894813873152</v>
+        <v>0.0963660037153204</v>
       </c>
       <c r="F18" t="n">
-        <v>0.725870178525637</v>
+        <v>0.924820580929298</v>
       </c>
       <c r="G18" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="19">
@@ -957,16 +939,16 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11348123242042</v>
+        <v>13.2380959383579</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0619651123381953</v>
+        <v>0.531828079165817</v>
       </c>
       <c r="F19" t="n">
-        <v>0.951610747354106</v>
+        <v>0.604551440164027</v>
       </c>
       <c r="G19" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="20">
@@ -980,16 +962,16 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>5.83692122891062</v>
+        <v>29.9276681567941</v>
       </c>
       <c r="E20" t="n">
-        <v>0.325766420989616</v>
+        <v>1.40340217464573</v>
       </c>
       <c r="F20" t="n">
-        <v>0.750211522848197</v>
+        <v>0.185840761869235</v>
       </c>
       <c r="G20" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="21">
@@ -1003,16 +985,16 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>22.3249201318602</v>
+        <v>19.2580008461087</v>
       </c>
       <c r="E21" t="n">
-        <v>1.19304362792561</v>
+        <v>0.880398130351539</v>
       </c>
       <c r="F21" t="n">
-        <v>0.255907614296882</v>
+        <v>0.395933718310799</v>
       </c>
       <c r="G21" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="22">
@@ -1026,16 +1008,16 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.78798922654816</v>
+        <v>-14.3330212283913</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0360847837662323</v>
+        <v>-0.832910453804778</v>
       </c>
       <c r="F22" t="n">
-        <v>0.971808079487335</v>
+        <v>0.421163664040512</v>
       </c>
       <c r="G22" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="23">
@@ -1049,16 +1031,16 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.31154284883609</v>
+        <v>-10.6264746919281</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.258762668246305</v>
+        <v>-0.482863852638451</v>
       </c>
       <c r="F23" t="n">
-        <v>0.800203548051438</v>
+        <v>0.637881708475833</v>
       </c>
       <c r="G23" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="24">
@@ -1072,16 +1054,16 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>2.31359024132614</v>
+        <v>-21.1274969694445</v>
       </c>
       <c r="E24" t="n">
-        <v>0.184009491330364</v>
+        <v>-1.56232365170755</v>
       </c>
       <c r="F24" t="n">
-        <v>0.857078845001714</v>
+        <v>0.144186083045671</v>
       </c>
       <c r="G24" t="n">
-        <v>0.971808079487335</v>
+        <v>0.951628148101427</v>
       </c>
     </row>
     <row r="25">
@@ -1095,16 +1077,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.57110411056</v>
+        <v>6.6521607610802</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.632961213317577</v>
+        <v>0.427937209428076</v>
       </c>
       <c r="F25" t="n">
-        <v>0.53863437476888</v>
+        <v>0.676276493308011</v>
       </c>
       <c r="G25" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="26">
@@ -1118,16 +1100,16 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.270018480673</v>
+        <v>-30.3663960142716</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.835293765276883</v>
+        <v>-2.37372781845641</v>
       </c>
       <c r="F26" t="n">
-        <v>0.419872482104705</v>
+        <v>0.0351620575347968</v>
       </c>
       <c r="G26" t="n">
-        <v>0.971808079487335</v>
+        <v>0.386782632882765</v>
       </c>
     </row>
     <row r="27">
@@ -1141,16 +1123,16 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>18.3518519928754</v>
+        <v>31.484456420315</v>
       </c>
       <c r="E27" t="n">
-        <v>0.911636133182421</v>
+        <v>2.01000257524371</v>
       </c>
       <c r="F27" t="n">
-        <v>0.379909738255773</v>
+        <v>0.0674599670215295</v>
       </c>
       <c r="G27" t="n">
-        <v>0.971808079487335</v>
+        <v>0.556544727927618</v>
       </c>
     </row>
     <row r="28">
@@ -1164,16 +1146,16 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>3.44665984365473</v>
+        <v>-16.4581465956347</v>
       </c>
       <c r="E28" t="n">
-        <v>0.136411071813056</v>
+        <v>-1.03511064344142</v>
       </c>
       <c r="F28" t="n">
-        <v>0.893758114036168</v>
+        <v>0.321027256007661</v>
       </c>
       <c r="G28" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="29">
@@ -1187,16 +1169,16 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-26.5780736331362</v>
+        <v>3.00969842232568</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.24039145813419</v>
+        <v>0.120136362003629</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0447655067496684</v>
+        <v>0.906363111196989</v>
       </c>
       <c r="G29" t="n">
-        <v>0.41035555572643</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="30">
@@ -1210,16 +1192,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-40.3410642365598</v>
+        <v>29.817070801179</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.38868986026447</v>
+        <v>2.81911955101653</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00538101890446403</v>
+        <v>0.0154852130383421</v>
       </c>
       <c r="G30" t="n">
-        <v>0.209859737274097</v>
+        <v>0.255506015132645</v>
       </c>
     </row>
     <row r="31">
@@ -1233,16 +1215,16 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>3.07245344196562</v>
+        <v>-3.93572134927756</v>
       </c>
       <c r="E31" t="n">
-        <v>0.210078984273806</v>
+        <v>-0.218086059294367</v>
       </c>
       <c r="F31" t="n">
-        <v>0.837130645765355</v>
+        <v>0.831026647406492</v>
       </c>
       <c r="G31" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="32">
@@ -1256,16 +1238,16 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-14.9883484917093</v>
+        <v>-18.3412748078537</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.933913431909142</v>
+        <v>-0.888655987641516</v>
       </c>
       <c r="F32" t="n">
-        <v>0.368760621504211</v>
+        <v>0.39165345964387</v>
       </c>
       <c r="G32" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="33">
@@ -1279,16 +1261,16 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.02125566107007</v>
+        <v>12.7751698945757</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.112900549904831</v>
+        <v>0.793139627484261</v>
       </c>
       <c r="F33" t="n">
-        <v>0.911976135697145</v>
+        <v>0.44309649855113</v>
       </c>
       <c r="G33" t="n">
-        <v>0.971808079487335</v>
+        <v>0.958801220623954</v>
       </c>
     </row>
     <row r="34">
@@ -1302,154 +1284,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>13.6326294291656</v>
+        <v>-40.1927229473046</v>
       </c>
       <c r="E34" t="n">
-        <v>0.862686193626119</v>
+        <v>-3.38773909640293</v>
       </c>
       <c r="F34" t="n">
-        <v>0.405221423975965</v>
+        <v>0.005390483807857</v>
       </c>
       <c r="G34" t="n">
-        <v>0.971808079487335</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>31.3231186812863</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.67539875932736</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0202080956343616</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.394057864870052</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>32.1784302517705</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.15035748286794</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.0526096866315935</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.41035555572643</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>5.33305939876674</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.195968148140426</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.847914448781185</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.971808079487335</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>25.4645048548767</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.18691293154553</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.0492797727187958</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.41035555572643</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>11.9372298231592</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.733139862143445</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.477551401096642</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.971808079487335</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-18.3654624061486</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.980443565764001</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.346221153697716</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.971808079487335</v>
+        <v>0.177885965659281</v>
       </c>
     </row>
   </sheetData>
@@ -1488,7 +1332,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1497,21 +1341,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1703.53150634579</v>
+        <v>295.616376056734</v>
       </c>
       <c r="E2" t="n">
-        <v>0.676385836954526</v>
+        <v>0.106559353197911</v>
       </c>
       <c r="F2" t="n">
-        <v>0.511622433770699</v>
+        <v>0.91689927400195</v>
       </c>
       <c r="G2" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1520,21 +1364,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-993.362964170442</v>
+        <v>2867.34101453239</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.333136095726755</v>
+        <v>0.513897065806869</v>
       </c>
       <c r="F3" t="n">
-        <v>0.74477986989833</v>
+        <v>0.616654999099279</v>
       </c>
       <c r="G3" t="n">
-        <v>0.884380164029874</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1543,21 +1387,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-4323.23334945328</v>
+        <v>-565.579532221148</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.41194269103905</v>
+        <v>-0.205508822285277</v>
       </c>
       <c r="F4" t="n">
-        <v>0.183369274716307</v>
+        <v>0.840619595373746</v>
       </c>
       <c r="G4" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1566,21 +1410,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>1745.91321873428</v>
+        <v>-941.569818110157</v>
       </c>
       <c r="E5" t="n">
-        <v>0.282383045141607</v>
+        <v>-0.410459063269655</v>
       </c>
       <c r="F5" t="n">
-        <v>0.782461250531492</v>
+        <v>0.688703158785334</v>
       </c>
       <c r="G5" t="n">
-        <v>0.884380164029874</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1589,21 +1433,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-276.841634002293</v>
+        <v>-568.173756042539</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.10886841487388</v>
+        <v>-0.223146613648183</v>
       </c>
       <c r="F6" t="n">
-        <v>0.915106151165086</v>
+        <v>0.8271747581773</v>
       </c>
       <c r="G6" t="n">
-        <v>0.93918789198522</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1612,21 +1456,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>3402.18637921034</v>
+        <v>1672.03990076253</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4910313256301</v>
+        <v>0.662897309614108</v>
       </c>
       <c r="F7" t="n">
-        <v>0.16176518831146</v>
+        <v>0.519926699284947</v>
       </c>
       <c r="G7" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1635,21 +1479,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>1949.21265516766</v>
+        <v>3811.56385475543</v>
       </c>
       <c r="E8" t="n">
-        <v>0.730509398419899</v>
+        <v>1.20222692861468</v>
       </c>
       <c r="F8" t="n">
-        <v>0.479099066465436</v>
+        <v>0.252462716788665</v>
       </c>
       <c r="G8" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1658,21 +1502,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>2551.51285336378</v>
+        <v>1334.18306742236</v>
       </c>
       <c r="E9" t="n">
-        <v>0.865887450447899</v>
+        <v>0.580092669047048</v>
       </c>
       <c r="F9" t="n">
-        <v>0.403531951318155</v>
+        <v>0.572583657436239</v>
       </c>
       <c r="G9" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1681,21 +1525,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-983.957465784976</v>
+        <v>-90.0463039717492</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.430823777041054</v>
+        <v>-0.0436895819525611</v>
       </c>
       <c r="F10" t="n">
-        <v>0.674233613109969</v>
+        <v>0.965870424420533</v>
       </c>
       <c r="G10" t="n">
-        <v>0.884380164029874</v>
+        <v>0.965870424420533</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1704,21 +1548,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>4735.01011690819</v>
+        <v>-729.344143101742</v>
       </c>
       <c r="E11" t="n">
-        <v>1.29871070326208</v>
+        <v>-0.268348628949391</v>
       </c>
       <c r="F11" t="n">
-        <v>0.218445381068175</v>
+        <v>0.79298843026081</v>
       </c>
       <c r="G11" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1727,21 +1571,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>1997.98046501088</v>
+        <v>-4034.07576383477</v>
       </c>
       <c r="E12" t="n">
-        <v>0.561329509582197</v>
+        <v>-1.31690089411246</v>
       </c>
       <c r="F12" t="n">
-        <v>0.584903488465423</v>
+        <v>0.212466688944954</v>
       </c>
       <c r="G12" t="n">
-        <v>0.877355232698134</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -1750,21 +1594,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-815.56123469999</v>
+        <v>3999.85041626302</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.300548805396788</v>
+        <v>0.950973240390624</v>
       </c>
       <c r="F13" t="n">
-        <v>0.768901976310338</v>
+        <v>0.360379435798206</v>
       </c>
       <c r="G13" t="n">
-        <v>0.884380164029874</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -1773,21 +1617,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>311.65650671836</v>
+        <v>-2989.41513976535</v>
       </c>
       <c r="E14" t="n">
-        <v>0.135987452548898</v>
+        <v>-1.01167549860435</v>
       </c>
       <c r="F14" t="n">
-        <v>0.894085845322661</v>
+        <v>0.331657885260318</v>
       </c>
       <c r="G14" t="n">
-        <v>0.93918789198522</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -1796,21 +1640,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>2953.72332843369</v>
+        <v>4047.02164586181</v>
       </c>
       <c r="E15" t="n">
-        <v>1.12714559774809</v>
+        <v>1.27513820078885</v>
       </c>
       <c r="F15" t="n">
-        <v>0.281715254227816</v>
+        <v>0.226395166229118</v>
       </c>
       <c r="G15" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -1819,21 +1663,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>4284.61765157729</v>
+        <v>-1115.56443640917</v>
       </c>
       <c r="E16" t="n">
-        <v>1.18269440369231</v>
+        <v>-0.330499601402058</v>
       </c>
       <c r="F16" t="n">
-        <v>0.259833929561488</v>
+        <v>0.746721410646738</v>
       </c>
       <c r="G16" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -1842,21 +1686,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>1827.89624032873</v>
+        <v>3123.43078877148</v>
       </c>
       <c r="E17" t="n">
-        <v>0.454953409005759</v>
+        <v>1.06468008950637</v>
       </c>
       <c r="F17" t="n">
-        <v>0.65726388318557</v>
+        <v>0.307975369466284</v>
       </c>
       <c r="G17" t="n">
-        <v>0.884380164029874</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -1865,21 +1709,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-3492.43274121206</v>
+        <v>2877.6524535746</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.982899046045594</v>
+        <v>1.08494913530519</v>
       </c>
       <c r="F18" t="n">
-        <v>0.345059749049539</v>
+        <v>0.299260171716668</v>
       </c>
       <c r="G18" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -1888,21 +1732,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>3130.62567711655</v>
+        <v>5577.08809126425</v>
       </c>
       <c r="E19" t="n">
-        <v>1.06994500358549</v>
+        <v>1.40213165625395</v>
       </c>
       <c r="F19" t="n">
-        <v>0.305693537715823</v>
+        <v>0.186210793433337</v>
       </c>
       <c r="G19" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -1911,21 +1755,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>2425.59821138577</v>
+        <v>4469.54561179349</v>
       </c>
       <c r="E20" t="n">
-        <v>0.812469056880813</v>
+        <v>1.20729739685015</v>
       </c>
       <c r="F20" t="n">
-        <v>0.432345754905374</v>
+        <v>0.250576335251853</v>
       </c>
       <c r="G20" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -1934,21 +1778,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>5289.92040486904</v>
+        <v>327.077413968488</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7593663872622</v>
+        <v>0.085076031036981</v>
       </c>
       <c r="F21" t="n">
-        <v>0.103960905504426</v>
+        <v>0.933603878764854</v>
       </c>
       <c r="G21" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -1957,21 +1801,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>3971.07782718711</v>
+        <v>-3462.61873962734</v>
       </c>
       <c r="E22" t="n">
-        <v>1.12173752439021</v>
+        <v>-1.21697394497601</v>
       </c>
       <c r="F22" t="n">
-        <v>0.283918996044579</v>
+        <v>0.247007181467981</v>
       </c>
       <c r="G22" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -1980,21 +1824,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-1330.6272075793</v>
+        <v>491.570428312545</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.381679378421132</v>
+        <v>0.129926336213294</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7093718101839</v>
+        <v>0.898777209086935</v>
       </c>
       <c r="G23" t="n">
-        <v>0.884380164029874</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -2003,21 +1847,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-1648.9184137262</v>
+        <v>-634.421964800774</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.788228175192736</v>
+        <v>-0.251644587520501</v>
       </c>
       <c r="F24" t="n">
-        <v>0.445855462767307</v>
+        <v>0.805573680147952</v>
       </c>
       <c r="G24" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -2026,21 +1870,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-4276.2788241082</v>
+        <v>-2126.81878107193</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.63451725787076</v>
+        <v>-0.818870922277542</v>
       </c>
       <c r="F25" t="n">
-        <v>0.128092685916151</v>
+        <v>0.428822998714246</v>
       </c>
       <c r="G25" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -2049,21 +1893,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-3373.43329188702</v>
+        <v>-2085.98101428628</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.1913475447963</v>
+        <v>-0.81074729350077</v>
       </c>
       <c r="F26" t="n">
-        <v>0.25654787483725</v>
+        <v>0.433296410601332</v>
       </c>
       <c r="G26" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -2072,21 +1916,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>-116.032885333493</v>
+        <v>1841.23505830153</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0327152667809868</v>
+        <v>0.605739826345329</v>
       </c>
       <c r="F27" t="n">
-        <v>0.974439508813005</v>
+        <v>0.555971601662265</v>
       </c>
       <c r="G27" t="n">
-        <v>0.974439508813005</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -2095,21 +1939,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>2672.62291796442</v>
+        <v>574.322550080391</v>
       </c>
       <c r="E28" t="n">
-        <v>0.630490496749633</v>
+        <v>0.203464001241737</v>
       </c>
       <c r="F28" t="n">
-        <v>0.540195266090027</v>
+        <v>0.842181801605536</v>
       </c>
       <c r="G28" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -2118,21 +1962,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-1582.85818342459</v>
+        <v>2594.41019752886</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.66969748079273</v>
+        <v>0.616963521887466</v>
       </c>
       <c r="F29" t="n">
-        <v>0.515730356009878</v>
+        <v>0.548786111112038</v>
       </c>
       <c r="G29" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -2141,21 +1985,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-4092.79528774749</v>
+        <v>4004.40853678823</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.58638132013475</v>
+        <v>1.98669770541738</v>
       </c>
       <c r="F30" t="n">
-        <v>0.13863817701333</v>
+        <v>0.0702746765503743</v>
       </c>
       <c r="G30" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -2164,21 +2008,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>-2423.89521904962</v>
+        <v>1403.07535980283</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.01141045111393</v>
+        <v>0.459367530893486</v>
       </c>
       <c r="F31" t="n">
-        <v>0.331779569733619</v>
+        <v>0.654180658504562</v>
       </c>
       <c r="G31" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -2187,21 +2031,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>768.63447594725</v>
+        <v>-2685.615555879</v>
       </c>
       <c r="E32" t="n">
-        <v>0.272222014467986</v>
+        <v>-0.757167032090871</v>
       </c>
       <c r="F32" t="n">
-        <v>0.790078653053584</v>
+        <v>0.463558298111568</v>
       </c>
       <c r="G32" t="n">
-        <v>0.884380164029874</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -2210,21 +2054,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>1119.60834582334</v>
+        <v>398.694356740607</v>
       </c>
       <c r="E33" t="n">
-        <v>0.368899857008685</v>
+        <v>0.141723054210782</v>
       </c>
       <c r="F33" t="n">
-        <v>0.718628919779833</v>
+        <v>0.889650280057536</v>
       </c>
       <c r="G33" t="n">
-        <v>0.884380164029874</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -2233,154 +2077,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>3074.32137890909</v>
+        <v>-4011.14291968877</v>
       </c>
       <c r="E34" t="n">
-        <v>1.16933113395569</v>
+        <v>-1.55492812982445</v>
       </c>
       <c r="F34" t="n">
-        <v>0.264973139129695</v>
+        <v>0.145929711122476</v>
       </c>
       <c r="G34" t="n">
-        <v>0.842704615100442</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>4585.34608921109</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.13759148424751</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0538217183281293</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.842704615100442</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1957.12189750513</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.664004043002693</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.519242388437648</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.842704615100442</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1238.41111494293</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.267435984182217</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.793674506180656</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.884380164029874</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1503.98636870513</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.652252614200848</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.526535224128728</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.842704615100442</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>316.821247811118</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.111778473419039</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.912847014740106</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.93918789198522</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-2568.30964274699</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.794351037216631</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.442417696815811</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.842704615100442</v>
+        <v>0.962778999976256</v>
       </c>
     </row>
   </sheetData>
@@ -2419,7 +2125,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2428,21 +2134,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1319.19383115366</v>
+        <v>354.939489676853</v>
       </c>
       <c r="E2" t="n">
-        <v>0.55962234342295</v>
+        <v>0.13753920856419</v>
       </c>
       <c r="F2" t="n">
-        <v>0.586031286892149</v>
+        <v>0.892885435799425</v>
       </c>
       <c r="G2" t="n">
-        <v>0.82785875534759</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2451,21 +2157,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-819.726064368263</v>
+        <v>4356.93957685826</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.295138905053103</v>
+        <v>0.854997233280525</v>
       </c>
       <c r="F3" t="n">
-        <v>0.77293192525209</v>
+        <v>0.409298762459517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.866348742990377</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2474,21 +2180,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-4817.30614772043</v>
+        <v>-428.246584377873</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.75522621912097</v>
+        <v>-0.167126407457634</v>
       </c>
       <c r="F4" t="n">
-        <v>0.104691163790679</v>
+        <v>0.870053840383621</v>
       </c>
       <c r="G4" t="n">
-        <v>0.808255218753333</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2497,21 +2203,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>3959.53995898734</v>
+        <v>-1478.19077234026</v>
       </c>
       <c r="E5" t="n">
-        <v>0.699811329894668</v>
+        <v>-0.701655112698016</v>
       </c>
       <c r="F5" t="n">
-        <v>0.497387826925128</v>
+        <v>0.496277623628839</v>
       </c>
       <c r="G5" t="n">
-        <v>0.808255218753333</v>
+        <v>0.909842309986205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2520,21 +2226,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-1229.14442923425</v>
+        <v>-1449.201811367</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.525127843562639</v>
+        <v>-0.620097867909427</v>
       </c>
       <c r="F6" t="n">
-        <v>0.60906006737566</v>
+        <v>0.54678875681419</v>
       </c>
       <c r="G6" t="n">
-        <v>0.82785875534759</v>
+        <v>0.930905054945765</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2543,21 +2249,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>3318.91064239481</v>
+        <v>1298.11088044217</v>
       </c>
       <c r="E7" t="n">
-        <v>1.57767912441861</v>
+        <v>0.550022801099624</v>
       </c>
       <c r="F7" t="n">
-        <v>0.140623223343006</v>
+        <v>0.592394125874578</v>
       </c>
       <c r="G7" t="n">
-        <v>0.808255218753333</v>
+        <v>0.930905054945765</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2566,21 +2272,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>2003.0764994734</v>
+        <v>3158.45430997302</v>
       </c>
       <c r="E8" t="n">
-        <v>0.810714035282047</v>
+        <v>1.0575073257841</v>
       </c>
       <c r="F8" t="n">
-        <v>0.433314787248326</v>
+        <v>0.311104503537554</v>
       </c>
       <c r="G8" t="n">
-        <v>0.808255218753333</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2589,21 +2295,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1952.07347353599</v>
+        <v>1746.89206114818</v>
       </c>
       <c r="E9" t="n">
-        <v>0.704823306866628</v>
+        <v>0.827696230999353</v>
       </c>
       <c r="F9" t="n">
-        <v>0.494373437154953</v>
+        <v>0.423997680432507</v>
       </c>
       <c r="G9" t="n">
-        <v>0.808255218753333</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2612,21 +2318,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-1507.25442117885</v>
+        <v>261.012789865324</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.718791575561277</v>
+        <v>0.136190579775009</v>
       </c>
       <c r="F10" t="n">
-        <v>0.486030846508877</v>
+        <v>0.893928694234485</v>
       </c>
       <c r="G10" t="n">
-        <v>0.808255218753333</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2635,21 +2341,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>4424.02737451301</v>
+        <v>-449.223555845703</v>
       </c>
       <c r="E11" t="n">
-        <v>1.30476291957051</v>
+        <v>-0.177325387584027</v>
       </c>
       <c r="F11" t="n">
-        <v>0.216441178135403</v>
+        <v>0.862210730026985</v>
       </c>
       <c r="G11" t="n">
-        <v>0.808255218753333</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2658,21 +2364,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>2049.87128129096</v>
+        <v>-4613.79501434321</v>
       </c>
       <c r="E12" t="n">
-        <v>0.620667297607685</v>
+        <v>-1.681853617915</v>
       </c>
       <c r="F12" t="n">
-        <v>0.546426325779185</v>
+        <v>0.11841498398717</v>
       </c>
       <c r="G12" t="n">
-        <v>0.82785875534759</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -2681,21 +2387,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-531.992859917182</v>
+        <v>3786.59777063496</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.210284344112785</v>
+        <v>0.96876912787058</v>
       </c>
       <c r="F13" t="n">
-        <v>0.836973954395807</v>
+        <v>0.351781406459037</v>
       </c>
       <c r="G13" t="n">
-        <v>0.882215789768553</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -2704,21 +2410,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>897.613742941754</v>
+        <v>-3084.32381684669</v>
       </c>
       <c r="E14" t="n">
-        <v>0.423716071217202</v>
+        <v>-1.13286487968938</v>
       </c>
       <c r="F14" t="n">
-        <v>0.679268722336484</v>
+        <v>0.279398971633163</v>
       </c>
       <c r="G14" t="n">
-        <v>0.82785875534759</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -2727,21 +2433,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>1488.73874114929</v>
+        <v>3505.50707267831</v>
       </c>
       <c r="E15" t="n">
-        <v>0.58889149850751</v>
+        <v>1.17639332199469</v>
       </c>
       <c r="F15" t="n">
-        <v>0.566854600204112</v>
+        <v>0.26224740808126</v>
       </c>
       <c r="G15" t="n">
-        <v>0.82785875534759</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -2750,21 +2456,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>3801.13186739244</v>
+        <v>-1195.22331744384</v>
       </c>
       <c r="E16" t="n">
-        <v>1.12164061555693</v>
+        <v>-0.381103169682883</v>
       </c>
       <c r="F16" t="n">
-        <v>0.283958605359721</v>
+        <v>0.709788171094844</v>
       </c>
       <c r="G16" t="n">
-        <v>0.808255218753333</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -2773,21 +2479,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>1716.27984568704</v>
+        <v>2304.12195380921</v>
       </c>
       <c r="E17" t="n">
-        <v>0.459138780980751</v>
+        <v>0.829612267040373</v>
       </c>
       <c r="F17" t="n">
-        <v>0.654340275335778</v>
+        <v>0.422954822376825</v>
       </c>
       <c r="G17" t="n">
-        <v>0.82785875534759</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -2796,21 +2502,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-3687.84708491994</v>
+        <v>1446.85653708432</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.12853751230548</v>
+        <v>0.566875783588296</v>
       </c>
       <c r="F18" t="n">
-        <v>0.281150185515886</v>
+        <v>0.581247356422876</v>
       </c>
       <c r="G18" t="n">
-        <v>0.808255218753333</v>
+        <v>0.930905054945765</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -2819,21 +2525,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>2248.01736772401</v>
+        <v>5785.22411751908</v>
       </c>
       <c r="E19" t="n">
-        <v>0.810178335233008</v>
+        <v>1.59508875884586</v>
       </c>
       <c r="F19" t="n">
-        <v>0.433610855495484</v>
+        <v>0.13667634611448</v>
       </c>
       <c r="G19" t="n">
-        <v>0.808255218753333</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -2842,21 +2548,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>2283.82647462501</v>
+        <v>4351.48996674499</v>
       </c>
       <c r="E20" t="n">
-        <v>0.822637504687987</v>
+        <v>1.27049656585645</v>
       </c>
       <c r="F20" t="n">
-        <v>0.426759188086854</v>
+        <v>0.22798769590674</v>
       </c>
       <c r="G20" t="n">
-        <v>0.808255218753333</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -2865,21 +2571,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>5209.01401240559</v>
+        <v>651.251556714558</v>
       </c>
       <c r="E21" t="n">
-        <v>1.89127143450063</v>
+        <v>0.182241427713013</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0829670925991915</v>
+        <v>0.858435666213427</v>
       </c>
       <c r="G21" t="n">
-        <v>0.808255218753333</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -2888,21 +2594,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>4103.19645064836</v>
+        <v>-2606.39023877194</v>
       </c>
       <c r="E22" t="n">
-        <v>1.26109976956865</v>
+        <v>-0.964089518819085</v>
       </c>
       <c r="F22" t="n">
-        <v>0.231239264154936</v>
+        <v>0.354028027995967</v>
       </c>
       <c r="G22" t="n">
-        <v>0.808255218753333</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -2911,21 +2617,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-1451.19153447958</v>
+        <v>316.804666565373</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.448359898775459</v>
+        <v>0.089953191312882</v>
       </c>
       <c r="F23" t="n">
-        <v>0.661881670840458</v>
+        <v>0.929808386526067</v>
       </c>
       <c r="G23" t="n">
-        <v>0.82785875534759</v>
+        <v>0.95739548042242</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -2934,21 +2640,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-1956.88537716514</v>
+        <v>-1021.35810260344</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.02200273132301</v>
+        <v>-0.437679342422318</v>
       </c>
       <c r="F24" t="n">
-        <v>0.326941946106468</v>
+        <v>0.669392676565137</v>
       </c>
       <c r="G24" t="n">
-        <v>0.808255218753333</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -2957,21 +2663,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-3558.55937444186</v>
+        <v>-2107.30238915736</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.43020818285427</v>
+        <v>-0.8752133498468</v>
       </c>
       <c r="F25" t="n">
-        <v>0.178175702408777</v>
+        <v>0.398637366807512</v>
       </c>
       <c r="G25" t="n">
-        <v>0.808255218753333</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -2980,21 +2686,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-2529.83401933529</v>
+        <v>-1968.23257078171</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.940828867254005</v>
+        <v>-0.822734446727619</v>
       </c>
       <c r="F26" t="n">
-        <v>0.365346807456895</v>
+        <v>0.426706157366354</v>
       </c>
       <c r="G26" t="n">
-        <v>0.808255218753333</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -3003,21 +2709,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>130.461552887962</v>
+        <v>2178.50536717073</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0395305877217926</v>
+        <v>0.777574665811689</v>
       </c>
       <c r="F27" t="n">
-        <v>0.96911743240086</v>
+        <v>0.451877839530257</v>
       </c>
       <c r="G27" t="n">
-        <v>0.991202517037786</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -3026,21 +2732,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>1741.02060697403</v>
+        <v>-143.508001863107</v>
       </c>
       <c r="E28" t="n">
-        <v>0.437703386074987</v>
+        <v>-0.0545489364056824</v>
       </c>
       <c r="F28" t="n">
-        <v>0.669375725667954</v>
+        <v>0.95739548042242</v>
       </c>
       <c r="G28" t="n">
-        <v>0.82785875534759</v>
+        <v>0.95739548042242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -3049,21 +2755,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-1697.74576479404</v>
+        <v>1640.05192776328</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.77672166168123</v>
+        <v>0.41559767727509</v>
       </c>
       <c r="F29" t="n">
-        <v>0.452362275557923</v>
+        <v>0.685039625308935</v>
       </c>
       <c r="G29" t="n">
-        <v>0.808255218753333</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -3072,21 +2778,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-3422.46512974556</v>
+        <v>3535.7050602347</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.39768177489322</v>
+        <v>1.8549833846807</v>
       </c>
       <c r="F30" t="n">
-        <v>0.187511643203146</v>
+        <v>0.0883209792090057</v>
       </c>
       <c r="G30" t="n">
-        <v>0.808255218753333</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -3095,21 +2801,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>-2327.20221573787</v>
+        <v>498.470006494862</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.04645178876474</v>
+        <v>0.174081707078666</v>
       </c>
       <c r="F31" t="n">
-        <v>0.315973761043759</v>
+        <v>0.864703530335748</v>
       </c>
       <c r="G31" t="n">
-        <v>0.808255218753333</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -3118,21 +2824,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-29.670471886454</v>
+        <v>-3606.4938616306</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0112581161939197</v>
+        <v>-1.12211832887045</v>
       </c>
       <c r="F32" t="n">
-        <v>0.991202517037786</v>
+        <v>0.283763391628804</v>
       </c>
       <c r="G32" t="n">
-        <v>0.991202517037786</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -3141,21 +2847,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>1006.28713539817</v>
+        <v>821.369354376379</v>
       </c>
       <c r="E33" t="n">
-        <v>0.356181748508565</v>
+        <v>0.314799538901948</v>
       </c>
       <c r="F33" t="n">
-        <v>0.727888073813271</v>
+        <v>0.75832029035719</v>
       </c>
       <c r="G33" t="n">
-        <v>0.860231359961138</v>
+        <v>0.951601513217355</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -3164,154 +2870,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>2237.28350882457</v>
+        <v>-3430.88409977336</v>
       </c>
       <c r="E34" t="n">
-        <v>0.894909059052901</v>
+        <v>-1.40747259690248</v>
       </c>
       <c r="F34" t="n">
-        <v>0.388433493602835</v>
+        <v>0.184659401607128</v>
       </c>
       <c r="G34" t="n">
-        <v>0.808255218753333</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>3946.25753100693</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.9247406534307</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0782936004312109</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.808255218753333</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2188.40863134368</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.804498594117372</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.436758024827648</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.808255218753333</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1085.71862002782</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.251883311369572</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.805393408757839</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.872509526154326</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1557.24217719211</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.728855810980922</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.480073555625779</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.808255218753333</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>760.051497553938</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.289027907173442</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.777492461658031</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.866348742990377</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-3350.97062401346</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-1.14321671203315</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.275243736817444</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.808255218753333</v>
+        <v>0.877174629676382</v>
       </c>
     </row>
   </sheetData>
@@ -3350,7 +2918,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -3359,21 +2927,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.17461173262586</v>
+        <v>-4.692600122439</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.05729488618309</v>
+        <v>-1.50716598108865</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3111975405498</v>
+        <v>0.157633902391521</v>
       </c>
       <c r="G2" t="n">
-        <v>0.551668367338282</v>
+        <v>0.349677457387881</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -3382,21 +2950,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.61233756548581</v>
+        <v>7.74272256060277</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.443554348088641</v>
+        <v>1.18597644682981</v>
       </c>
       <c r="F3" t="n">
-        <v>0.665256442210409</v>
+        <v>0.258583711821548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.831291889483345</v>
+        <v>0.474070138339504</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -3405,21 +2973,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>3.78598104863016</v>
+        <v>0.882618285250027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.972116867987275</v>
+        <v>0.262442689822527</v>
       </c>
       <c r="F4" t="n">
-        <v>0.350180463479144</v>
+        <v>0.797431367048706</v>
       </c>
       <c r="G4" t="n">
-        <v>0.588357996225763</v>
+        <v>0.868985407432981</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -3428,21 +2996,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>9.21892465650882</v>
+        <v>4.59227991637139</v>
       </c>
       <c r="E5" t="n">
-        <v>1.29717181498701</v>
+        <v>1.84006436664206</v>
       </c>
       <c r="F5" t="n">
-        <v>0.218957379399698</v>
+        <v>0.0906118422327052</v>
       </c>
       <c r="G5" t="n">
-        <v>0.426966889829411</v>
+        <v>0.271835526698116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -3451,21 +3019,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.17781373469988</v>
+        <v>-4.30216101887985</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4560570152861</v>
+        <v>-1.50232804954726</v>
       </c>
       <c r="F6" t="n">
-        <v>0.171037474090356</v>
+        <v>0.158863095701594</v>
       </c>
       <c r="G6" t="n">
-        <v>0.370581193862437</v>
+        <v>0.349677457387881</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -3474,21 +3042,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.288320558247254</v>
+        <v>-3.38167646037694</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0949083570142054</v>
+        <v>-1.13243907611627</v>
       </c>
       <c r="F7" t="n">
-        <v>0.925954035340784</v>
+        <v>0.279570915255416</v>
       </c>
       <c r="G7" t="n">
-        <v>0.95032124679712</v>
+        <v>0.485168289055393</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -3497,21 +3065,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.50048295095342</v>
+        <v>-5.82160400049942</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.87475989407626</v>
+        <v>-1.55417105537174</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0853653885590273</v>
+        <v>0.146109228315623</v>
       </c>
       <c r="G8" t="n">
-        <v>0.256096165677082</v>
+        <v>0.349677457387881</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -3520,21 +3088,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.0050258173856</v>
+        <v>-3.31229652026402</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.82709271161572</v>
+        <v>-1.23232798597923</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0926473355814469</v>
+        <v>0.241426531526472</v>
       </c>
       <c r="G9" t="n">
-        <v>0.258089006262602</v>
+        <v>0.468651502374915</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -3543,21 +3111,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>4.67230652570565</v>
+        <v>0.888588262500514</v>
       </c>
       <c r="E10" t="n">
-        <v>1.89049547017652</v>
+        <v>0.354227038622511</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0830784093121248</v>
+        <v>0.729315189612526</v>
       </c>
       <c r="G10" t="n">
-        <v>0.256096165677082</v>
+        <v>0.829910388179771</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -3566,21 +3134,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.42800624239352</v>
+        <v>0.789998901402064</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.515325118681965</v>
+        <v>0.237441639132603</v>
       </c>
       <c r="F11" t="n">
-        <v>0.615686662623495</v>
+        <v>0.816319625164316</v>
       </c>
       <c r="G11" t="n">
-        <v>0.824300345638017</v>
+        <v>0.868985407432981</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -3589,21 +3157,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>6.86258850804427</v>
+        <v>3.48009087987465</v>
       </c>
       <c r="E12" t="n">
-        <v>1.74118585009252</v>
+        <v>0.896632266489965</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1072019576898</v>
+        <v>0.387549349340476</v>
       </c>
       <c r="G12" t="n">
-        <v>0.262932159974905</v>
+        <v>0.556060420996573</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -3612,21 +3180,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>0.666604272261301</v>
+        <v>-8.92715246963572</v>
       </c>
       <c r="E13" t="n">
-        <v>0.200386460933581</v>
+        <v>-1.91064107222043</v>
       </c>
       <c r="F13" t="n">
-        <v>0.844534307578098</v>
+        <v>0.0802322009465605</v>
       </c>
       <c r="G13" t="n">
-        <v>0.935789007801002</v>
+        <v>0.271835526698116</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -3635,21 +3203,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.150583290325819</v>
+        <v>9.58813059437724</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0536737645894389</v>
+        <v>3.75463717751715</v>
       </c>
       <c r="F14" t="n">
-        <v>0.958078302003137</v>
+        <v>0.00274764313281138</v>
       </c>
       <c r="G14" t="n">
-        <v>0.958078302003137</v>
+        <v>0.0640840645380952</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -3658,21 +3226,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.57067395805607</v>
+        <v>0.620312990760724</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.47328205762518</v>
+        <v>0.1500691517066</v>
       </c>
       <c r="F15" t="n">
-        <v>0.166416038673157</v>
+        <v>0.883202920264724</v>
       </c>
       <c r="G15" t="n">
-        <v>0.370581193862437</v>
+        <v>0.883202920264724</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -3681,21 +3249,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.26479204332753</v>
+        <v>1.68266648783838</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.488388919036503</v>
+        <v>0.408460291319462</v>
       </c>
       <c r="F16" t="n">
-        <v>0.634077188952321</v>
+        <v>0.690130404166715</v>
       </c>
       <c r="G16" t="n">
-        <v>0.824300345638017</v>
+        <v>0.813367976339343</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -3704,21 +3272,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.4003725953943</v>
+        <v>-6.86997504320969</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.39131941551852</v>
+        <v>-2.15485021490642</v>
       </c>
       <c r="F17" t="n">
-        <v>0.189384712438646</v>
+        <v>0.0521892853942291</v>
       </c>
       <c r="G17" t="n">
-        <v>0.388737041321431</v>
+        <v>0.215280802251195</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -3727,21 +3295,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>12.1218730431815</v>
+        <v>-4.68562573577369</v>
       </c>
       <c r="E18" t="n">
-        <v>4.24057394642642</v>
+        <v>-1.50200957253129</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00114629491254044</v>
+        <v>0.158944298812673</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0447055015890773</v>
+        <v>0.349677457387881</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -3750,21 +3318,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.86042103917625</v>
+        <v>-4.5566409205826</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.15728116081322</v>
+        <v>-0.896616830454789</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0519631347293173</v>
+        <v>0.387557263118824</v>
       </c>
       <c r="G19" t="n">
-        <v>0.19840802100414</v>
+        <v>0.556060420996573</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -3773,21 +3341,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.656597221313545</v>
+        <v>2.35053158766913</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.175250352660316</v>
+        <v>0.495061916850986</v>
       </c>
       <c r="F20" t="n">
-        <v>0.863805237970155</v>
+        <v>0.629496738221303</v>
       </c>
       <c r="G20" t="n">
-        <v>0.935789007801002</v>
+        <v>0.769384902270481</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -3796,21 +3364,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.71911293584677</v>
+        <v>7.76568123204883</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.41974957855437</v>
+        <v>1.87747483151344</v>
       </c>
       <c r="F21" t="n">
-        <v>0.682085652909411</v>
+        <v>0.0849667511214219</v>
       </c>
       <c r="G21" t="n">
-        <v>0.831291889483345</v>
+        <v>0.271835526698116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -3819,21 +3387,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.07004428925844</v>
+        <v>-0.659069866728696</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.73750185513151</v>
+        <v>-0.178879410113768</v>
       </c>
       <c r="F22" t="n">
-        <v>0.107869604092269</v>
+        <v>0.861016995529844</v>
       </c>
       <c r="G22" t="n">
-        <v>0.262932159974905</v>
+        <v>0.883202920264724</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -3842,21 +3410,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>3.06141717892537</v>
+        <v>-5.48137692445656</v>
       </c>
       <c r="E23" t="n">
-        <v>0.729125828217579</v>
+        <v>-1.25918217864358</v>
       </c>
       <c r="F23" t="n">
-        <v>0.479914346242706</v>
+        <v>0.231907354280237</v>
       </c>
       <c r="G23" t="n">
-        <v>0.693209611239465</v>
+        <v>0.468651502374915</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -3865,21 +3433,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>5.20668218244312</v>
+        <v>-6.16405465889862</v>
       </c>
       <c r="E24" t="n">
-        <v>2.41990234274481</v>
+        <v>-2.43725543352036</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0323232086472047</v>
+        <v>0.0313145490183991</v>
       </c>
       <c r="G24" t="n">
-        <v>0.171649886298649</v>
+        <v>0.147625731086738</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -3888,21 +3456,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>6.38994525472397</v>
+        <v>8.11206718368336</v>
       </c>
       <c r="E25" t="n">
-        <v>2.11570236671833</v>
+        <v>3.56556954267642</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0559612366934755</v>
+        <v>0.0038838826992785</v>
       </c>
       <c r="G25" t="n">
-        <v>0.19840802100414</v>
+        <v>0.0640840645380952</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -3911,21 +3479,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.830241072200107</v>
+        <v>-6.7534386225135</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.227128954964381</v>
+        <v>-2.61899959564859</v>
       </c>
       <c r="F26" t="n">
-        <v>0.824146853573052</v>
+        <v>0.0224262662510609</v>
       </c>
       <c r="G26" t="n">
-        <v>0.935789007801002</v>
+        <v>0.147625731086738</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -3934,21 +3502,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>7.89158415343856</v>
+        <v>7.59504139579195</v>
       </c>
       <c r="E27" t="n">
-        <v>2.13688349972808</v>
+        <v>2.47149578511342</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0538896990477896</v>
+        <v>0.0294127963724323</v>
       </c>
       <c r="G27" t="n">
-        <v>0.19840802100414</v>
+        <v>0.147625731086738</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -3957,21 +3525,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.57093682909104</v>
+        <v>-6.93948680441162</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.10982530307682</v>
+        <v>-2.4607521499324</v>
       </c>
       <c r="F28" t="n">
-        <v>0.288819531779492</v>
+        <v>0.0299971454468616</v>
       </c>
       <c r="G28" t="n">
-        <v>0.536379130447628</v>
+        <v>0.147625731086738</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -3980,21 +3548,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-6.32186891960977</v>
+        <v>-5.46609781211913</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.73508451784029</v>
+        <v>-1.09729999333758</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0180953269951206</v>
+        <v>0.294041387306299</v>
       </c>
       <c r="G29" t="n">
-        <v>0.14583276483777</v>
+        <v>0.485168289055393</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -4003,21 +3571,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-6.83493081628147</v>
+        <v>2.82334006800508</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.3930179748697</v>
+        <v>1.03676756928666</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0339480364007197</v>
+        <v>0.320285249081431</v>
       </c>
       <c r="G30" t="n">
-        <v>0.171649886298649</v>
+        <v>0.503305391413678</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -4026,21 +3594,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>7.4787448159286</v>
+        <v>-2.91195440647585</v>
       </c>
       <c r="E31" t="n">
-        <v>3.46167035644623</v>
+        <v>-0.792503442704996</v>
       </c>
       <c r="F31" t="n">
-        <v>0.00470264398333348</v>
+        <v>0.443453247557403</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0917015576750029</v>
+        <v>0.585358286775772</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -4049,21 +3617,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-6.78318778742054</v>
+        <v>2.22154197864116</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.3729756173004</v>
+        <v>0.505461348882009</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0352102330869024</v>
+        <v>0.622390429951915</v>
       </c>
       <c r="G32" t="n">
-        <v>0.171649886298649</v>
+        <v>0.769384902270481</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -4072,21 +3640,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-3.4125692399785</v>
+        <v>2.85343367237199</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.947516977277809</v>
+        <v>0.85317435754597</v>
       </c>
       <c r="F33" t="n">
-        <v>0.362066459215854</v>
+        <v>0.410269434145216</v>
       </c>
       <c r="G33" t="n">
-        <v>0.588357996225763</v>
+        <v>0.564120471949673</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -4095,154 +3663,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.458600200081937</v>
+        <v>-6.95931098749777</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.135196696309822</v>
+        <v>-2.47134686056684</v>
       </c>
       <c r="F34" t="n">
-        <v>0.894697665199188</v>
+        <v>0.0294208205554177</v>
       </c>
       <c r="G34" t="n">
-        <v>0.943059701155901</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2.44337580389523</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.81394594967967</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.431531389477399</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.671020006878743</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>7.84982809795117</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.71743062847544</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.0186965083125346</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.14583276483777</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-3.06227644688113</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.545600628056552</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.595337263699149</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.824300345638017</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>6.29855103272979</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.83573502265967</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.0150150884538202</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.14583276483777</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2.65790073066333</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.785581693816564</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.447346671252495</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.671020006878743</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1.48801354485722</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.368752949183773</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.718735610544307</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.849414812461454</v>
+        <v>0.147625731086738</v>
       </c>
     </row>
   </sheetData>
@@ -4281,7 +3711,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -4290,21 +3720,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>44.8014674550621</v>
+        <v>85.5202817326253</v>
       </c>
       <c r="E2" t="n">
-        <v>0.822420429666235</v>
+        <v>1.54657236859337</v>
       </c>
       <c r="F2" t="n">
-        <v>0.426877951521893</v>
+        <v>0.147921605509702</v>
       </c>
       <c r="G2" t="n">
-        <v>0.996399716604058</v>
+        <v>0.610176622727521</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -4313,21 +3743,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>44.3907148868141</v>
+        <v>10.3484831071104</v>
       </c>
       <c r="E3" t="n">
-        <v>0.692618084004251</v>
+        <v>0.0841103812942413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.501733370910791</v>
+        <v>0.934355569779212</v>
       </c>
       <c r="G3" t="n">
-        <v>0.996399716604058</v>
+        <v>0.973086016272408</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -4336,21 +3766,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-72.267544505117</v>
+        <v>-4.88872715005611</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.04644380438636</v>
+        <v>-0.0812951091029788</v>
       </c>
       <c r="F4" t="n">
-        <v>0.315977297959099</v>
+        <v>0.936547437496859</v>
       </c>
       <c r="G4" t="n">
-        <v>0.996399716604058</v>
+        <v>0.973086016272408</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -4359,21 +3789,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-26.8555295762617</v>
+        <v>-80.0935494423025</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.198746870697868</v>
+        <v>-1.78843048587312</v>
       </c>
       <c r="F5" t="n">
-        <v>0.845788269792952</v>
+        <v>0.098961765581015</v>
       </c>
       <c r="G5" t="n">
-        <v>0.999162452827931</v>
+        <v>0.610176622727521</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -4382,21 +3812,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>82.0928061303019</v>
+        <v>79.798596533655</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6354181343303</v>
+        <v>1.57457488304278</v>
       </c>
       <c r="F6" t="n">
-        <v>0.127902205611055</v>
+        <v>0.141337270268202</v>
       </c>
       <c r="G6" t="n">
-        <v>0.831364336471856</v>
+        <v>0.610176622727521</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -4405,21 +3835,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.521376937845043</v>
+        <v>45.3524079863932</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.00961943784364925</v>
+        <v>0.832446716967266</v>
       </c>
       <c r="F7" t="n">
-        <v>0.992482990776052</v>
+        <v>0.421415203356338</v>
       </c>
       <c r="G7" t="n">
-        <v>0.999162452827931</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -4428,21 +3858,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>41.9362536604355</v>
+        <v>86.9447009825459</v>
       </c>
       <c r="E8" t="n">
-        <v>0.719886960990203</v>
+        <v>1.26400359532922</v>
       </c>
       <c r="F8" t="n">
-        <v>0.485380275357273</v>
+        <v>0.230230507176689</v>
       </c>
       <c r="G8" t="n">
-        <v>0.996399716604058</v>
+        <v>0.690691521530067</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -4451,21 +3881,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>71.8029913361407</v>
+        <v>22.2095074241619</v>
       </c>
       <c r="E9" t="n">
-        <v>1.14071249554685</v>
+        <v>0.440013631573926</v>
       </c>
       <c r="F9" t="n">
-        <v>0.276244544172147</v>
+        <v>0.667747879272063</v>
       </c>
       <c r="G9" t="n">
-        <v>0.996399716604058</v>
+        <v>0.948645118621414</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -4474,21 +3904,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-80.4273402038426</v>
+        <v>-28.4089361398406</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.80632478609339</v>
+        <v>-0.642467624977267</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0959924804214705</v>
+        <v>0.532652527932709</v>
       </c>
       <c r="G10" t="n">
-        <v>0.74874134728747</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -4497,21 +3927,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>74.2372629138445</v>
+        <v>-2.04882109107796</v>
       </c>
       <c r="E11" t="n">
-        <v>0.90304119669157</v>
+        <v>-0.0344483465752148</v>
       </c>
       <c r="F11" t="n">
-        <v>0.384273215300244</v>
+        <v>0.973086016272408</v>
       </c>
       <c r="G11" t="n">
-        <v>0.996399716604058</v>
+        <v>0.973086016272408</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -4520,21 +3950,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>3.84380171849087</v>
+        <v>-65.1347373181713</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0488627388758233</v>
+        <v>-0.944159646735828</v>
       </c>
       <c r="F12" t="n">
-        <v>0.96183253843376</v>
+        <v>0.363710533577564</v>
       </c>
       <c r="G12" t="n">
-        <v>0.999162452827931</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -4543,21 +3973,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.38588229939314</v>
+        <v>151.045198231688</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0233206877151497</v>
+        <v>1.78565178050633</v>
       </c>
       <c r="F13" t="n">
-        <v>0.981777777049276</v>
+        <v>0.0994301955060893</v>
       </c>
       <c r="G13" t="n">
-        <v>0.999162452827931</v>
+        <v>0.610176622727521</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -4566,21 +3996,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.4949309748354</v>
+        <v>-39.1835235160528</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.331122718402454</v>
+        <v>-0.591845632648545</v>
       </c>
       <c r="F14" t="n">
-        <v>0.746262376621463</v>
+        <v>0.564938092757456</v>
       </c>
       <c r="G14" t="n">
-        <v>0.999162452827931</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -4589,21 +4019,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>29.9528326142893</v>
+        <v>108.024064907289</v>
       </c>
       <c r="E15" t="n">
-        <v>0.503394841605404</v>
+        <v>1.61527069703268</v>
       </c>
       <c r="F15" t="n">
-        <v>0.623799421214464</v>
+        <v>0.132221952852063</v>
       </c>
       <c r="G15" t="n">
-        <v>0.996399716604058</v>
+        <v>0.610176622727521</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -4612,21 +4042,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>156.585529741129</v>
+        <v>21.4385503496388</v>
       </c>
       <c r="E16" t="n">
-        <v>2.22947744718757</v>
+        <v>0.290806549761568</v>
       </c>
       <c r="F16" t="n">
-        <v>0.045653673368411</v>
+        <v>0.776164187962975</v>
       </c>
       <c r="G16" t="n">
-        <v>0.690420728691391</v>
+        <v>0.948645118621414</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -4635,21 +4065,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>44.3108512913667</v>
+        <v>101.189321685893</v>
       </c>
       <c r="E17" t="n">
-        <v>0.506501224923544</v>
+        <v>1.6793127631754</v>
       </c>
       <c r="F17" t="n">
-        <v>0.621682008858857</v>
+        <v>0.118917577762137</v>
       </c>
       <c r="G17" t="n">
-        <v>0.996399716604058</v>
+        <v>0.610176622727521</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -4658,21 +4088,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-47.4085691056277</v>
+        <v>31.4793207752029</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.596971934022744</v>
+        <v>0.525029569700474</v>
       </c>
       <c r="F18" t="n">
-        <v>0.561620751210196</v>
+        <v>0.609126322012746</v>
       </c>
       <c r="G18" t="n">
-        <v>0.996399716604058</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -4681,21 +4111,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>90.782684006044</v>
+        <v>203.68002014824</v>
       </c>
       <c r="E19" t="n">
-        <v>1.47705162666107</v>
+        <v>2.79555175676114</v>
       </c>
       <c r="F19" t="n">
-        <v>0.16541891199989</v>
+        <v>0.0161771472020417</v>
       </c>
       <c r="G19" t="n">
-        <v>0.921619652570817</v>
+        <v>0.533845857667376</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -4704,21 +4134,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>40.6011513977894</v>
+        <v>101.729090448019</v>
       </c>
       <c r="E20" t="n">
-        <v>0.616370162639747</v>
+        <v>1.26622374955746</v>
       </c>
       <c r="F20" t="n">
-        <v>0.549164685194789</v>
+        <v>0.229461634100489</v>
       </c>
       <c r="G20" t="n">
-        <v>0.996399716604058</v>
+        <v>0.690691521530067</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -4727,21 +4157,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>137.58179987909</v>
+        <v>7.95013553344776</v>
       </c>
       <c r="E21" t="n">
-        <v>2.22127275683779</v>
+        <v>0.0947846378713608</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0463323469608408</v>
+        <v>0.926050246208163</v>
       </c>
       <c r="G21" t="n">
-        <v>0.690420728691391</v>
+        <v>0.973086016272408</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -4750,21 +4180,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>148.065796949227</v>
+        <v>-110.980159047924</v>
       </c>
       <c r="E22" t="n">
-        <v>2.14506213125114</v>
+        <v>-1.93100375494254</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0531092868224147</v>
+        <v>0.0774463254086945</v>
       </c>
       <c r="G22" t="n">
-        <v>0.690420728691391</v>
+        <v>0.610176622727521</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -4773,21 +4203,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>20.1494275984761</v>
+        <v>45.8424222661986</v>
       </c>
       <c r="E23" t="n">
-        <v>0.264069421098171</v>
+        <v>0.562204670273981</v>
       </c>
       <c r="F23" t="n">
-        <v>0.796206857709456</v>
+        <v>0.584325776493124</v>
       </c>
       <c r="G23" t="n">
-        <v>0.999162452827931</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -4796,21 +4226,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-54.5465048348128</v>
+        <v>36.961371472145</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.23740054481806</v>
+        <v>0.68308251542704</v>
       </c>
       <c r="F24" t="n">
-        <v>0.239604990827786</v>
+        <v>0.507528783567288</v>
       </c>
       <c r="G24" t="n">
-        <v>0.996399716604058</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -4819,21 +4249,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-50.4887633311668</v>
+        <v>17.845535382479</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.822135691963467</v>
+        <v>0.307672637334593</v>
       </c>
       <c r="F25" t="n">
-        <v>0.427033766705942</v>
+        <v>0.763606039388318</v>
       </c>
       <c r="G25" t="n">
-        <v>0.996399716604058</v>
+        <v>0.948645118621414</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -4842,21 +4272,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-107.706973287855</v>
+        <v>18.4563074993819</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.87446220151278</v>
+        <v>0.32149735940046</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0854092026502161</v>
+        <v>0.75336436981219</v>
       </c>
       <c r="G26" t="n">
-        <v>0.74874134728747</v>
+        <v>0.948645118621414</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -4865,21 +4295,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>4.01497612079177</v>
+        <v>-54.5224576442616</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0518867974972051</v>
+        <v>-0.832896641411976</v>
       </c>
       <c r="F27" t="n">
-        <v>0.959472626588692</v>
+        <v>0.421171154696849</v>
       </c>
       <c r="G27" t="n">
-        <v>0.999162452827931</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -4888,21 +4318,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>12.935200070147</v>
+        <v>40.6148926788427</v>
       </c>
       <c r="E28" t="n">
-        <v>0.137706775928169</v>
+        <v>0.670551500055482</v>
       </c>
       <c r="F28" t="n">
-        <v>0.892755825332311</v>
+        <v>0.515204751339223</v>
       </c>
       <c r="G28" t="n">
-        <v>0.999162452827931</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -4911,21 +4341,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>28.803466947358</v>
+        <v>15.4967551384386</v>
       </c>
       <c r="E29" t="n">
-        <v>0.555392562660833</v>
+        <v>0.166477957970506</v>
       </c>
       <c r="F29" t="n">
-        <v>0.588830489015943</v>
+        <v>0.87055300203324</v>
       </c>
       <c r="G29" t="n">
-        <v>0.996399716604058</v>
+        <v>0.973086016272408</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -4934,21 +4364,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-24.2909536369333</v>
+        <v>3.51172982313052</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.394883435872138</v>
+        <v>0.0692832252412993</v>
       </c>
       <c r="F30" t="n">
-        <v>0.699857825327292</v>
+        <v>0.945905324874729</v>
       </c>
       <c r="G30" t="n">
-        <v>0.999162452827931</v>
+        <v>0.973086016272408</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -4957,21 +4387,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>17.8727379030516</v>
+        <v>51.2525932963526</v>
       </c>
       <c r="E31" t="n">
-        <v>0.329588948350977</v>
+        <v>0.781567550008097</v>
       </c>
       <c r="F31" t="n">
-        <v>0.747392447486918</v>
+        <v>0.449614616878079</v>
       </c>
       <c r="G31" t="n">
-        <v>0.999162452827931</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -4980,21 +4410,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>39.5462809618695</v>
+        <v>97.3717326536555</v>
       </c>
       <c r="E32" t="n">
-        <v>0.651159860085155</v>
+        <v>1.31475239389931</v>
       </c>
       <c r="F32" t="n">
-        <v>0.527216369777029</v>
+        <v>0.21316583827703</v>
       </c>
       <c r="G32" t="n">
-        <v>0.996399716604058</v>
+        <v>0.690691521530067</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -5003,21 +4433,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-12.433594073866</v>
+        <v>-48.1070391741106</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.186980897847903</v>
+        <v>-0.803918313625173</v>
       </c>
       <c r="F33" t="n">
-        <v>0.854799648395182</v>
+        <v>0.437080395385429</v>
       </c>
       <c r="G33" t="n">
-        <v>0.999162452827931</v>
+        <v>0.913689483019119</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -5026,154 +4456,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>28.88308969898</v>
+        <v>-18.4492860426378</v>
       </c>
       <c r="E34" t="n">
-        <v>0.481651799397954</v>
+        <v>-0.300166591321005</v>
       </c>
       <c r="F34" t="n">
-        <v>0.638717767053883</v>
+        <v>0.769186465863434</v>
       </c>
       <c r="G34" t="n">
-        <v>0.996399716604058</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>10.0980346268462</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.183871378019306</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.857184816763929</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.999162452827931</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-43.7494007798486</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.680921271019326</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.508847817852724</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.996399716604058</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>40.7141462692123</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.404506985187665</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.692956969885038</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.999162452827931</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0548687090984412</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.00107178264502068</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.999162452827931</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.999162452827931</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-49.9320842680084</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.82983035573966</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.422836228852181</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.996399716604058</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>89.8107739959942</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.32911462492579</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.208527633321518</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.996399716604058</v>
+        <v>0.948645118621414</v>
       </c>
     </row>
   </sheetData>
@@ -5212,7 +4504,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B2" t="n">
         <v>13</v>
@@ -5221,21 +4513,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>7.09109396182945</v>
+        <v>3.68456056186861</v>
       </c>
       <c r="E2" t="n">
-        <v>0.704115126383551</v>
+        <v>0.274705107159925</v>
       </c>
       <c r="F2" t="n">
-        <v>0.49599701756945</v>
+        <v>0.788633657963397</v>
       </c>
       <c r="G2" t="n">
-        <v>0.849797730825689</v>
+        <v>0.897410714234211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
         <v>13</v>
@@ -5244,21 +4536,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>12.1437131953955</v>
+        <v>19.4960380557391</v>
       </c>
       <c r="E3" t="n">
-        <v>0.741042093441772</v>
+        <v>0.905204673349941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.474190856232794</v>
+        <v>0.384754797726184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.849797730825689</v>
+        <v>0.869842540157188</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B4" t="n">
         <v>13</v>
@@ -5267,21 +4559,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0924014382356798</v>
+        <v>16.3781320157653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0070678689101303</v>
+        <v>1.23812472445804</v>
       </c>
       <c r="F4" t="n">
-        <v>0.994487257112147</v>
+        <v>0.241443578254941</v>
       </c>
       <c r="G4" t="n">
-        <v>0.994487257112147</v>
+        <v>0.827685947649401</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
@@ -5290,21 +4582,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>16.2311897866932</v>
+        <v>5.38419815371051</v>
       </c>
       <c r="E5" t="n">
-        <v>0.673658691851263</v>
+        <v>0.526184129208018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.514434157634214</v>
+        <v>0.609205428684185</v>
       </c>
       <c r="G5" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
@@ -5313,21 +4605,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-15.259576583175</v>
+        <v>-15.1060346555657</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.57733010737937</v>
+        <v>-1.55339119400486</v>
       </c>
       <c r="F6" t="n">
-        <v>0.143023938201828</v>
+        <v>0.148610644018964</v>
       </c>
       <c r="G6" t="n">
-        <v>0.849797730825689</v>
+        <v>0.827685947649401</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -5336,21 +4628,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>15.2707844157787</v>
+        <v>7.22755960055728</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7414309246855</v>
+        <v>0.715836230962657</v>
       </c>
       <c r="F7" t="n">
-        <v>0.109463505145082</v>
+        <v>0.489009888286233</v>
       </c>
       <c r="G7" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>13</v>
@@ -5359,21 +4651,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>12.5883424672194</v>
+        <v>-0.930364826463662</v>
       </c>
       <c r="E8" t="n">
-        <v>1.09015297428712</v>
+        <v>-0.0694989470364007</v>
       </c>
       <c r="F8" t="n">
-        <v>0.298950611906727</v>
+        <v>0.945839806484756</v>
       </c>
       <c r="G8" t="n">
-        <v>0.849797730825689</v>
+        <v>0.945839806484756</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B9" t="n">
         <v>13</v>
@@ -5382,21 +4674,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.72626903081884</v>
+        <v>11.8476707423398</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.143352804028413</v>
+        <v>1.21224303397878</v>
       </c>
       <c r="F9" t="n">
-        <v>0.888603888147484</v>
+        <v>0.250813923530121</v>
       </c>
       <c r="G9" t="n">
-        <v>0.981779726893473</v>
+        <v>0.827685947649401</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -5405,21 +4697,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>5.57207738641152</v>
+        <v>16.9710045367877</v>
       </c>
       <c r="E10" t="n">
-        <v>0.554545655717084</v>
+        <v>2.3307725844024</v>
       </c>
       <c r="F10" t="n">
-        <v>0.590302236111076</v>
+        <v>0.0398148173029601</v>
       </c>
       <c r="G10" t="n">
-        <v>0.852658785493776</v>
+        <v>0.656944485498842</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -5428,21 +4720,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.3889827900002</v>
+        <v>-24.981866555447</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.758254425121613</v>
+        <v>-2.38399803699084</v>
       </c>
       <c r="F11" t="n">
-        <v>0.464234838986211</v>
+        <v>0.0362440265229769</v>
       </c>
       <c r="G11" t="n">
-        <v>0.849797730825689</v>
+        <v>0.656944485498842</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -5451,21 +4743,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>20.4911965586022</v>
+        <v>-5.44080497918172</v>
       </c>
       <c r="E12" t="n">
-        <v>1.11808831339661</v>
+        <v>-0.423644313596641</v>
       </c>
       <c r="F12" t="n">
-        <v>0.28735303672626</v>
+        <v>0.679990456604229</v>
       </c>
       <c r="G12" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B13" t="n">
         <v>13</v>
@@ -5474,21 +4766,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-24.6345158977542</v>
+        <v>-20.5846558411393</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.37463418272704</v>
+        <v>-1.2414158054402</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0368489064305526</v>
+        <v>0.240272435177789</v>
       </c>
       <c r="G13" t="n">
-        <v>0.807421340076303</v>
+        <v>0.827685947649401</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B14" t="n">
         <v>13</v>
@@ -5497,21 +4789,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>18.6492707234533</v>
+        <v>14.9868603137053</v>
       </c>
       <c r="E14" t="n">
-        <v>2.19428545537011</v>
+        <v>1.31975629918646</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0505884061232295</v>
+        <v>0.213723343043472</v>
       </c>
       <c r="G14" t="n">
-        <v>0.807421340076303</v>
+        <v>0.827685947649401</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B15" t="n">
         <v>13</v>
@@ -5520,21 +4812,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.2084297468404</v>
+        <v>-7.70291962245183</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.369838492004732</v>
+        <v>-0.580249322883198</v>
       </c>
       <c r="F15" t="n">
-        <v>0.718524489902885</v>
+        <v>0.573440523015965</v>
       </c>
       <c r="G15" t="n">
-        <v>0.875701722069141</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B16" t="n">
         <v>13</v>
@@ -5543,21 +4835,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-12.5446422304494</v>
+        <v>5.09942533251801</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.856369800347902</v>
+        <v>0.361867620433074</v>
       </c>
       <c r="F16" t="n">
-        <v>0.41006097159583</v>
+        <v>0.724306412227947</v>
       </c>
       <c r="G16" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
         <v>13</v>
@@ -5566,21 +4858,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-19.0689955945364</v>
+        <v>-10.3295295064512</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2753291013834</v>
+        <v>-0.827451552951254</v>
       </c>
       <c r="F17" t="n">
-        <v>0.228468808970874</v>
+        <v>0.425568106322018</v>
       </c>
       <c r="G17" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B18" t="n">
         <v>13</v>
@@ -5589,21 +4881,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>19.3942832466161</v>
+        <v>-4.4298402875046</v>
       </c>
       <c r="E18" t="n">
-        <v>1.44070074735793</v>
+        <v>-0.385742522991143</v>
       </c>
       <c r="F18" t="n">
-        <v>0.177521290060288</v>
+        <v>0.707043116411099</v>
       </c>
       <c r="G18" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B19" t="n">
         <v>13</v>
@@ -5612,21 +4904,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-11.3273604923011</v>
+        <v>3.63280094061448</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.902503637932342</v>
+        <v>0.214852585978933</v>
       </c>
       <c r="F19" t="n">
-        <v>0.386125479630821</v>
+        <v>0.833813595818396</v>
       </c>
       <c r="G19" t="n">
-        <v>0.849797730825689</v>
+        <v>0.917194955400235</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B20" t="n">
         <v>13</v>
@@ -5635,21 +4927,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-21.6057391777103</v>
+        <v>13.8886696396476</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.90805993533523</v>
+        <v>0.923997587453551</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0828124451360311</v>
+        <v>0.375312132275514</v>
       </c>
       <c r="G20" t="n">
-        <v>0.807421340076303</v>
+        <v>0.869842540157188</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B21" t="n">
         <v>13</v>
@@ -5658,21 +4950,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>6.26735776263528</v>
+        <v>13.2893467137505</v>
       </c>
       <c r="E21" t="n">
-        <v>0.47515726817933</v>
+        <v>0.884433232631444</v>
       </c>
       <c r="F21" t="n">
-        <v>0.643969689406007</v>
+        <v>0.395382972798722</v>
       </c>
       <c r="G21" t="n">
-        <v>0.875701722069141</v>
+        <v>0.869842540157188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B22" t="n">
         <v>13</v>
@@ -5681,21 +4973,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.745758586542816</v>
+        <v>5.1185714244824</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0501403923194015</v>
+        <v>0.429078764418196</v>
       </c>
       <c r="F22" t="n">
-        <v>0.960909389134283</v>
+        <v>0.67614871724189</v>
       </c>
       <c r="G22" t="n">
-        <v>0.986196478322027</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B23" t="n">
         <v>13</v>
@@ -5704,21 +4996,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>8.42450654644011</v>
+        <v>-22.364165258981</v>
       </c>
       <c r="E23" t="n">
-        <v>0.580469519607127</v>
+        <v>-1.6765261375452</v>
       </c>
       <c r="F23" t="n">
-        <v>0.573297204161237</v>
+        <v>0.121791548494408</v>
       </c>
       <c r="G23" t="n">
-        <v>0.852658785493776</v>
+        <v>0.827685947649401</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B24" t="n">
         <v>13</v>
@@ -5727,21 +5019,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>5.5080440868875</v>
+        <v>-3.97328476175767</v>
       </c>
       <c r="E24" t="n">
-        <v>0.662556695695691</v>
+        <v>-0.393443005445029</v>
       </c>
       <c r="F24" t="n">
-        <v>0.521254923109533</v>
+        <v>0.70151100955846</v>
       </c>
       <c r="G24" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B25" t="n">
         <v>13</v>
@@ -5750,21 +5042,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>11.9552757664085</v>
+        <v>3.665962230306</v>
       </c>
       <c r="E25" t="n">
-        <v>1.05465502204979</v>
+        <v>0.335040195397447</v>
       </c>
       <c r="F25" t="n">
-        <v>0.314197508903817</v>
+        <v>0.743896884701265</v>
       </c>
       <c r="G25" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B26" t="n">
         <v>13</v>
@@ -5773,21 +5065,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>4.63323299437398</v>
+        <v>-9.20659594597505</v>
       </c>
       <c r="E26" t="n">
-        <v>0.389994218466429</v>
+        <v>-0.900627332976118</v>
       </c>
       <c r="F26" t="n">
-        <v>0.703986445358331</v>
+        <v>0.387079639486912</v>
       </c>
       <c r="G26" t="n">
-        <v>0.875701722069141</v>
+        <v>0.869842540157188</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B27" t="n">
         <v>13</v>
@@ -5796,21 +5088,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>12.7982309176628</v>
+        <v>8.2454291632263</v>
       </c>
       <c r="E27" t="n">
-        <v>0.946226691415878</v>
+        <v>0.682983742275317</v>
       </c>
       <c r="F27" t="n">
-        <v>0.364355328612507</v>
+        <v>0.508746219584368</v>
       </c>
       <c r="G27" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B28" t="n">
         <v>13</v>
@@ -5819,21 +5111,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>17.5205046743824</v>
+        <v>-6.14111063973503</v>
       </c>
       <c r="E28" t="n">
-        <v>1.04212917830258</v>
+        <v>-0.536799015896914</v>
       </c>
       <c r="F28" t="n">
-        <v>0.319714764024291</v>
+        <v>0.602094520566324</v>
       </c>
       <c r="G28" t="n">
-        <v>0.849797730825689</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B29" t="n">
         <v>13</v>
@@ -5842,21 +5134,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-7.28493618410555</v>
+        <v>17.1593282318859</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.779040725793569</v>
+        <v>1.02951153616404</v>
       </c>
       <c r="F29" t="n">
-        <v>0.452389992717577</v>
+        <v>0.325345218512089</v>
       </c>
       <c r="G29" t="n">
-        <v>0.849797730825689</v>
+        <v>0.869842540157188</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B30" t="n">
         <v>13</v>
@@ -5865,21 +5157,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-12.5944058247184</v>
+        <v>14.8194318835486</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.19476318738997</v>
+        <v>1.83126149631023</v>
       </c>
       <c r="F30" t="n">
-        <v>0.257304674323742</v>
+        <v>0.0942564696510949</v>
       </c>
       <c r="G30" t="n">
-        <v>0.849797730825689</v>
+        <v>0.827685947649401</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B31" t="n">
         <v>13</v>
@@ -5888,21 +5180,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>2.87012814314956</v>
+        <v>7.72185928296859</v>
       </c>
       <c r="E31" t="n">
-        <v>0.274720284986654</v>
+        <v>0.646363952908438</v>
       </c>
       <c r="F31" t="n">
-        <v>0.788622295392714</v>
+        <v>0.53129792134047</v>
       </c>
       <c r="G31" t="n">
-        <v>0.932008167282299</v>
+        <v>0.876735614112205</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B32" t="n">
         <v>13</v>
@@ -5911,21 +5203,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.90794124717096</v>
+        <v>-2.46347476633285</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.425954226099228</v>
+        <v>-0.16859997253107</v>
       </c>
       <c r="F32" t="n">
-        <v>0.678356358884512</v>
+        <v>0.869171467073236</v>
       </c>
       <c r="G32" t="n">
-        <v>0.875701722069141</v>
+        <v>0.925247045594089</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B33" t="n">
         <v>13</v>
@@ -5934,21 +5226,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>5.21914967632722</v>
+        <v>-1.20744756976628</v>
       </c>
       <c r="E33" t="n">
-        <v>0.396002893217005</v>
+        <v>-0.106554497375709</v>
       </c>
       <c r="F33" t="n">
-        <v>0.69967593226027</v>
+        <v>0.917060871588512</v>
       </c>
       <c r="G33" t="n">
-        <v>0.875701722069141</v>
+        <v>0.945719023825653</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B34" t="n">
         <v>13</v>
@@ -5957,154 +5249,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>12.3904765581803</v>
+        <v>-14.0134022471332</v>
       </c>
       <c r="E34" t="n">
-        <v>1.19923806188121</v>
+        <v>-1.35456413573687</v>
       </c>
       <c r="F34" t="n">
-        <v>0.255630485276497</v>
+        <v>0.20272516391519</v>
       </c>
       <c r="G34" t="n">
-        <v>0.849797730825689</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" t="n">
-        <v>13</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>16.5074098265513</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.91232117172661</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0822165657875346</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.807421340076303</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" t="n">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>7.34908305363097</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.624961718579349</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.544742135144673</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.849797730825689</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" t="n">
-        <v>13</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1.31603926918712</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.0620396583174184</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.951644175838701</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.986196478322027</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" t="n">
-        <v>13</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>5.752516696536</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.632112533516672</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.540228827954566</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.849797730825689</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" t="n">
-        <v>13</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-1.37500216298419</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.120502202495679</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.90625820944013</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.981779726893473</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" t="n">
-        <v>13</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-2.44416621499886</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.183657295105447</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.857623954700201</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.981779726893473</v>
+        <v>0.827685947649401</v>
       </c>
     </row>
   </sheetData>
@@ -6120,123 +5274,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>10.57110411056</v>
+        <v>10.6264746919281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>11.3273604923011</v>
+        <v>8.2454291632263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>41.9362536604355</v>
+        <v>45.3524079863932</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -6245,24 +5399,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1997.98046501088</v>
+        <v>2085.98101428628</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -6271,33 +5425,33 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2003.0764994734</v>
+        <v>1746.89206114818</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.57067395805607</v>
+        <v>4.59227991637139</v>
       </c>
     </row>
   </sheetData>
